--- a/medford_vnutripolostnye_datchiki_uzi.xlsx
+++ b/medford_vnutripolostnye_datchiki_uzi.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Chison, Canon, GE, Samsung, Mindray — всего 20 позиций.</t>
+          <t>Внутриполостные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Chison, Canon, GE, Samsung, Mindray.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_vnutripolostnye_datchiki_uzi.xlsx
+++ b/medford_vnutripolostnye_datchiki_uzi.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать внутриполостные датчики УЗИ для клиники?</t>
+          <t>Что такое внутриполостной датчик УЗИ?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диапазон частот, МГц, Количество элементов, Радиус кривизны, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Это ультразвуковой преобразователь, который вводят в естественную полость тела (влагалище, прямую кишку) вплотную к исследуемому органу. В отличие от абдоминального датчика, прикладываемого к коже, он подводится через тонкую слизистую, что позволяет применять высокие частоты и получать изображение с высоким разрешением.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Почему внутриполостной датчик даёт более чёткое изображение?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>При трансабдоминальном сканировании ультразвук проходит кожу, жир, мышцы и газ кишечника, поэтому используют низкие частоты 2–5 МГц с меньшей детализацией. Внутриполостной датчик подведён вплотную к органу, между ними лишь слизистая, что позволяет применять частоты 5–9 МГц и выше и различать структуры менее 1 мм.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какие бывают типы внутриполостных датчиков?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены SonoScape, Chison, Canon, GE, Samsung, Mindray. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Трансвагинальный (TV) — для гинекологии и акушерства, визуализации эндометрия, яичников, шейки матки. Трансректальный (TR) — для ТРУЗИ простаты, торцевой или боковой. Биплановый совмещает две решётки для одновременного продольного и поперечного среза. Комбинированные вводят и вагинально, и ректально. Отдельно выделяют чреспищеводные для кардиологии.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Что такое биплановый датчик?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Биплановый датчик содержит в одном корпусе две решётки пьезоэлементов: одна даёт поперечный срез, другая продольный. Это позволяет видеть орган, например простату, сразу в двух ортогональных проекциях на одном экране в реальном времени, что критично при прицельной биопсии и брахитерапии.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>На сколько вводят датчик при УЗИ малого таза?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Рабочая часть внутриполостного датчика — тонкая трубка длиной около 12–15 см с малым диаметром. Глубину и технику введения определяет врач исходя из вида исследования и анатомии пациента. Конкретные цифры зависят от методики; решение и выполнение процедуры остаются за специалистом.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Как работает датчик УЗИ?</t>
+          <t>Как обрабатывают внутриполостной датчик?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Датчик нельзя автоклавировать или кипятить — высокая температура разрушает пьезокристаллы. После каждого пациента применяют химическую дезинфекцию (салфетки, спреи, замачивание в растворах), а перед исследованием надевают одноразовый чехол. Правильная обработка обязательна для безопасности и сохранности датчика.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>На сколько см вводят датчик при УЗИ малого таза?</t>
+          <t>Можно ли поставить датчик от другого аппарата?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Только при подтверждённой совместимости. Датчик проектируется под конкретную платформу с определённым разъёмом и протоколом. Модель GE не подойдёт к сканеру Samsung или Mindray без совместимости. Перед покупкой сверьте марку, модель аппарата и тип коннектора.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Chison, Canon, GE, Samsung, Mindray.</t>
+          <t>Внутриполостные датчики УЗИ — преобразователи, которые вводят в естественные полости тела (влагалище, прямую кишку) вплотную к органу для исследования с высоким разрешением. Близость к тканям позволяет применять высокие частоты — в каталоге от 2 до 13 МГц, поэтому изображение детальнее, чем при трансабдоминальном сканировании. Представлены микроконвексные и объёмные модели GE, Samsung, Mindray, Canon, SonoScape, Chison и SIUI с числом элементов 128–256 и малым радиусом кривизны 10–13 мм, дающим широкий угол обзора. Тип датчика подбирают под исследование и совместимость с моделью аппарата.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы внутриполостных датчиков</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое внутриполостные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4502,215 +4502,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы внутриполостных датчиков</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Область применения</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диапазон частот, МГц</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Количество элементов</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус кривизны, мм</t>
+          <t>Особенность</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостной датчик УЗИ Sonoscape 6V5A</t>
+          <t>Трансвагинальный (TV)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>Гинекология, акушерство</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>4,0-9,0</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Осмотр эндометрия, яичников, шейки матки</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостной датчик УЗИ Chison D6C12L</t>
+          <t>Трансректальный (TR)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Chison</t>
+          <t>Урология, ТРУЗИ простаты</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4,0-6,0</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Торцевой или боковой</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостной датчик Canon PVT-781VT</t>
+          <t>Биплановый</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Canon</t>
+          <t>Урология, биопсия, брахитерапия</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>3,0-11,0</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Два ортогональных среза одновременно</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостной датчик УЗИ Sonoscape 6V4</t>
+          <t>Комбинированный</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>Вагинально и ректально</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>4,0-9,0</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>Универсальное введение</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостной датчик SonoScape VE9-5</t>
+          <t>Объёмный 3D/4D</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>Акушерство, гинекология</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2.0–13.0</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Внутриполостной объемный датчик GE RIC5-9-D</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>3-10</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Трёхмерная реконструкция</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4722,7 +4633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5048,12 +4959,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите вид исследования</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается внутриполостные датчики УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Трансвагинальное УЗИ в гинекологии и акушерстве, трансректальное УЗИ простаты в урологии и объёмная 3D/4D-визуализация требуют разных датчиков. С определения задачи начинается подбор типа и частотного диапазона.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5093,12 +5004,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите тип датчика</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Трансвагинальный (TV) — для эндометрия, яичников и шейки матки. Трансректальный (TR) — для простаты, торцевой или боковой. Биплановый даёт два ортогональных среза сразу, что важно при биопсии и брахитерапии. Комбинированные вводят и ректально, и вагинально.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5138,12 +5049,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сопоставьте частоту и радиус кривизны</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диапазон частот, МГц, Количество элементов, Радиус кривизны, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Высокая частота даёт детализацию: в каталоге модели от 2 до 13 МГц. Малый радиус кривизны 10–13 мм формирует широкий угол обзора — врач осматривает большую область, поворачивая рукоятку. Сопоставьте параметры с задачами кабинета.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5183,12 +5094,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте совместимость с аппаратом</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: SonoScape, Chison, Canon, GE, Samsung, Mindray.</t>
+          <t>Внутриполостной датчик рассчитан на конкретную платформу и разъём. Датчик GE, Samsung, Mindray или Canon не заработает на чужой системе без совместимости. Уточните точную марку и модель сканера до заказа, иначе датчик не распознается.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5228,12 +5139,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените необходимость 3D/4D</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Объёмные внутриполостные датчики (GE RIC5-9-D, RIC6-12, Samsung EV3-10B) строят трёхмерную реконструкцию, что востребовано в акушерстве и оценке объёмных образований. Если методики 3D/4D в кабинете не применяются, достаточно микроконвексной модели, что снижает стоимость.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5273,12 +5184,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Учтите обработку и расходники</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Датчик нельзя автоклавировать или кипятить — высокая температура разрушает пьезокристаллы. Между пациентами применяют химическую дезинфекцию, а перед исследованием надевают одноразовый чехол (презерватив для УЗИ). Заложите совместимые дезсредства и расходники в план эксплуатации.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5328,7 +5239,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостные датчики УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены SonoScape, Chison, Canon, GE, Samsung, Mindray. При выборе обращают внимание на диапазон частот, количество элементов, радиус кривизны, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Внутриполостной датчик выигрывает за счёт близости к органу: между ним и тканью только слизистая, поэтому можно поднять частоту и получить детализацию, недоступную абдоминальному датчику. Для гинекологии берут трансвагинальный, для простаты — трансректальный, а объёмные модели вроде GE RIC5-9-D или Samsung EV3-10B добавляют 3D/4D для акушерства. Обязательно сверяйте совместимость с аппаратом и помните: датчик нельзя автоклавировать, только химическая дезинфекция и одноразовый чехол на каждого пациента.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5612,13 +5523,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое внутриполостные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Внутриполостные датчики УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов SonoScape, Chison, Canon, GE, Samsung, Mindray. Подберём вариант под задачи вашего отделения.</t>
+          <t>Внутриполостной датчик УЗИ вводят в естественную полость тела вплотную к органу, что позволяет работать на высоких частотах (5–13 МГц) и различать структуры менее 1 мм — детальнее, чем при трансабдоминальном сканировании. Основные типы: трансвагинальный (гинекология, акушерство), трансректальный (урология, ТРУЗИ простаты), биплановый (два ортогональных среза одновременно) и комбинированный. В каталоге — микроконвексные и объёмные 3D/4D датчики GE, Samsung, Mindray, Canon, SonoScape, Chison и SIUI с малым радиусом кривизны 10–13 мм, числом элементов 128–256 и широким углом обзора.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5655,13 +5566,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое внутриполостной датчик УЗИ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диапазон частот, МГц, Количество элементов, Радиус кривизны, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Внутриполостной датчик — специализированный ультразвуковой преобразователь, который вводят в полости тела вплотную к органу. Такой доступ убирает помехи от кожи, жира и газа кишечника и позволяет применять высокие частоты. В результате изображение детальнее, чем при трансабдоминальном сканировании, что важно в гинекологии, акушерстве и урологии.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5698,13 +5609,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Как устроен датчик</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Конструкция продиктована анатомией: эргономичная рукоятка с меткой ориентации, длинная тонкая рабочая часть (около 12–15 см) и сканирующая головка на кончике. Головка чаще микроконвексная, с малым радиусом кривизны 8–13 мм, что даёт широкий угол обзора до 150–180° — врач осматривает большую область, поворачивая рукоятку.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5741,13 +5652,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Типы внутриполостных датчиков</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Трансвагинальные применяют в гинекологии и акушерстве, трансректальные — в урологии для ТРУЗИ простаты. Биплановые дают два ортогональных среза одновременно для прицельной биопсии и брахитерапии. Комбинированные вводят и ректально, и вагинально. Часть моделей поддерживает 3D/4D-визуализацию и специализированные насадки для биопсии.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5764,6 +5675,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как выбрать внутриполостной датчик</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Сначала уточните точную марку и модель аппарата и тип разъёма — датчик работает только на совместимой платформе. Затем определите тип под исследование (трансвагинальный, трансректальный, биплановый) и решите, нужна ли 3D/4D-визуализация. В каталоге — датчики GE, Samsung, Mindray, Canon, SonoScape, Chison и SIUI с частотами 2–13 МГц.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>vnutripolostnye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
